--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Requestors</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>What is it?</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Strategic Importance of Solution</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Value Proposition</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Experience Intent (if any)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>New Threshold (Acceptable to Ship)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Target (Design Goal)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Impacted Programs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Partners</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
@@ -491,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Automatic Firmware Update Scheduling</t>
+          <t>Enable Automatic Firmware Update for Printer Fleet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allow users to schedule automatic firmware updates for their devices, providing flexibility in update timing.</t>
+          <t>Implement automatic firmware update capability across all managed printers in the fleet.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reduces manual intervention and ensures devices are kept up-to-date with minimal disruption.</t>
+          <t>Ensures printers are always running the latest firmware, reducing security risks and improving reliability.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Improved device reliability, enhanced security, and reduced support calls due to outdated firmware.</t>
+          <t>Minimizes manual intervention, decreases downtime, and enhances overall fleet security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should be able to set preferred update windows and receive notifications before updates occur.</t>
+          <t>Users should not need to manually check or initiate firmware updates.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Firmware update scheduling functionality for all supported devices.</t>
+          <t>All managed printers within enterprise environments.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Scheduling interface available; updates occur within user-defined windows.</t>
+          <t>Automatic updates enabled for 90% of printers.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Seamless, user-driven firmware update scheduling with minimal impact on device operation.</t>
+          <t>Achieve 100% automatic update coverage for managed printers.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,69 +558,69 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Device management backend; notification system</t>
+          <t>Printer management software; network connectivity; firmware update server</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Firmware Team; Device Management Team</t>
+          <t>IT Operations; Firmware Engineering; Security Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Support for Multi-Language Error Messages</t>
+          <t>Add Support for Secure Print Release</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maria Lopez</t>
+          <t>Emily Chen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Localization</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Display firmware error messages in multiple languages based on user preference.</t>
+          <t>Introduce secure print release functionality requiring user authentication before printing.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves accessibility and user satisfaction for global customers.</t>
+          <t>Protects sensitive documents from unauthorized access and reduces waste.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reduces confusion, increases supportability, and enhances user experience for non-English speakers.</t>
+          <t>Improves document security and compliance with enterprise privacy standards.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Error messages should automatically appear in the user's selected language.</t>
+          <t>Users must authenticate at the device before their print job is released.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Localization of all firmware error messages for supported languages.</t>
+          <t>All printers with badge reader or PIN entry capability.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Core error messages localized in top 5 languages.</t>
+          <t>Secure print release available on 80% of devices.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Full localization coverage for all error messages.</t>
+          <t>Secure print release on all enterprise printers.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,69 +630,69 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Localization libraries; language selection mechanism</t>
+          <t>Authentication system; badge reader hardware; firmware integration</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Team; Localization Team</t>
+          <t>Security Team; Hardware Engineering; Firmware Team</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Implement Secure Boot Verification</t>
+          <t>Improve Printer Boot Time</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alex Chen</t>
+          <t>Raj Patel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Add secure boot verification to ensure only authorized firmware is loaded during device startup.</t>
+          <t>Optimize firmware to reduce printer boot time by at least 20%.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Protects devices from unauthorized firmware and potential security breaches.</t>
+          <t>Faster boot times improve user productivity and reduce frustration.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhanced device security, compliance with industry standards, and reduced risk of malicious firmware.</t>
+          <t>Enhanced user experience and quicker recovery from power cycles.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Device should not boot if firmware fails secure verification.</t>
+          <t>Printers should be ready to use within seconds after power-on.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Secure boot verification for all new device models.</t>
+          <t>All enterprise printer models.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Secure boot enabled and verified on all new devices.</t>
+          <t>Boot time reduced by 20% compared to previous firmware.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Zero tolerance for unauthorized firmware loading.</t>
+          <t>Boot time under 30 seconds for all models.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,69 +702,69 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cryptographic libraries; hardware support for secure boot</t>
+          <t>Firmware optimization; hardware readiness; QA testing</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware Team; Security Team; Hardware Team</t>
+          <t>Firmware Engineering; QA Team</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Optimize Firmware Power Consumption During Idle</t>
+          <t>Add Multi-Language Support for Printer UI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Maria Lopez</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduce power consumption of firmware when device is idle.</t>
+          <t>Enable multi-language support in printer user interface, covering top 5 languages used in target markets.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Extends device battery life and reduces energy costs.</t>
+          <t>Expands market reach and improves accessibility for global users.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lower operational costs, improved sustainability, and better user satisfaction.</t>
+          <t>Better user satisfaction and reduced support calls in non-English regions.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Device should automatically enter low-power mode when not in use.</t>
+          <t>Users can select their preferred language during setup or from settings.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Idle power optimization for all firmware-controlled devices.</t>
+          <t>All printers shipped to international markets.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Idle power reduced by at least 10% compared to previous release.</t>
+          <t>Support for English, Spanish, French, German, and Japanese.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Achieve best-in-class idle power consumption.</t>
+          <t>Support for 10 languages in UI.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -762,69 +774,69 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Power management subsystem</t>
+          <t>Localization files; UI firmware updates</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Firmware Team; Power Management Team</t>
+          <t>Localization Team; Firmware Engineering</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Provide Firmware Rollback Capability</t>
+          <t>Implement Energy Saving Mode</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Michael Brown</t>
+          <t>Alex Kim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Allow users to rollback to a previous firmware version if issues are encountered.</t>
+          <t>Add firmware-controlled energy saving mode that reduces power consumption during idle periods.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Minimizes downtime and user frustration after problematic updates.</t>
+          <t>Supports corporate sustainability goals and reduces operational costs.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Improved reliability, faster recovery from update failures, and reduced support escalations.</t>
+          <t>Lower energy bills and improved environmental footprint.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Users should be able to initiate rollback easily via device interface.</t>
+          <t>Printers automatically enter energy saving mode when idle.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Rollback functionality for all firmware updates.</t>
+          <t>All enterprise printers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Rollback available for last firmware version.</t>
+          <t>Energy saving mode reduces idle power by 30%.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Seamless rollback with no data loss.</t>
+          <t>Idle power consumption below 5W.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -834,17 +846,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Firmware version management; user interface</t>
+          <t>Firmware power management; hardware support</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Firmware Team; Device Management Team</t>
+          <t>Firmware Engineering; Sustainability Team</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>WANT</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Automatic Firmware Update for Printer Fleet</t>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,42 +513,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Update Management</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement automatic firmware update capability across all managed printers in the fleet.</t>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ensures printers are always running the latest firmware, reducing security risks and improving reliability.</t>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security requirements.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Minimizes manual intervention, decreases downtime, and enhances overall fleet security.</t>
+          <t>Reduces risk of firmware attacks, improves compliance with industry standards, and increases customer trust in device security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should not need to manually check or initiate firmware updates.</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>All managed printers within enterprise environments.</t>
+          <t>Embedded controller firmware; Secure Boot implementation; signature verification at boot.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Automatic updates enabled for 90% of printers.</t>
+          <t>Firmware must reject unsigned images and boot only signed firmware.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Achieve 100% automatic update coverage for managed printers.</t>
+          <t>100% of shipped devices support Secure Boot for embedded controller firmware.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Printer management software; network connectivity; firmware update server</t>
+          <t>Secure Boot infrastructure; signing tools; hardware support for signature verification.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IT Operations; Firmware Engineering; Security Team</t>
+          <t>Platform Security Team; Embedded Controller Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Support for Secure Print Release</t>
+          <t>Optimize Power Management for Sleep Mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Introduce secure print release functionality requiring user authentication before printing.</t>
+          <t>Improve firmware handling of sleep mode to minimize power consumption while maintaining wake responsiveness.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Protects sensitive documents from unauthorized access and reduces waste.</t>
+          <t>Extends battery life and meets customer expectations for efficient power usage in portable devices.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Improves document security and compliance with enterprise privacy standards.</t>
+          <t>Longer battery runtime, reduced energy costs, and improved user satisfaction.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users must authenticate at the device before their print job is released.</t>
+          <t>Device should wake quickly from sleep without noticeable delay.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All printers with badge reader or PIN entry capability.</t>
+          <t>Firmware power management routines; sleep/wake transitions; battery-powered devices.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Secure print release available on 80% of devices.</t>
+          <t>Sleep mode power draw must not exceed 0.5W.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Secure print release on all enterprise printers.</t>
+          <t>Achieve sleep mode power draw of 0.3W or less.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Authentication system; badge reader hardware; firmware integration</t>
+          <t>Hardware power rails; OS sleep signals; battery management IC.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Security Team; Hardware Engineering; Firmware Team</t>
+          <t>Power Management Firmware Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -647,52 +647,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Improve Printer Boot Time</t>
+          <t>Add Support for Multi-Language Error Messages</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Carlos Ruiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Optimize firmware to reduce printer boot time by at least 20%.</t>
+          <t>Implement multi-language support for firmware error messages to improve accessibility for global users.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Faster boot times improve user productivity and reduce frustration.</t>
+          <t>Addresses international market needs and reduces support calls due to unclear error communication.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhanced user experience and quicker recovery from power cycles.</t>
+          <t>Better user experience for non-English speakers, increased global adoption, and fewer misunderstandings.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Printers should be ready to use within seconds after power-on.</t>
+          <t>Users should see error messages in their preferred language as set in device settings.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All enterprise printer models.</t>
+          <t>Firmware error handling; language selection logic; message translation.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Boot time reduced by 20% compared to previous firmware.</t>
+          <t>Support for English, Spanish, French, and German error messages.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Boot time under 30 seconds for all models.</t>
+          <t>Support for 10+ languages in firmware error messages.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,159 +702,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Firmware optimization; hardware readiness; QA testing</t>
+          <t>Translation files; language selection mechanism; QA for localization.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware Engineering; QA Team</t>
+          <t>Localization Team; Firmware QA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Add Multi-Language Support for Printer UI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Maria Lopez</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Localization</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Enable multi-language support in printer user interface, covering top 5 languages used in target markets.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Expands market reach and improves accessibility for global users.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Better user satisfaction and reduced support calls in non-English regions.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Users can select their preferred language during setup or from settings.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>All printers shipped to international markets.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Support for English, Spanish, French, German, and Japanese.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Support for 10 languages in UI.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Localization files; UI firmware updates</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Localization Team; Firmware Engineering</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Implement Energy Saving Mode</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Alex Kim</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Sustainability</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Add firmware-controlled energy saving mode that reduces power consumption during idle periods.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Supports corporate sustainability goals and reduces operational costs.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lower energy bills and improved environmental footprint.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Printers automatically enter energy saving mode when idle.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>All enterprise printers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Energy saving mode reduces idle power by 30%.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Idle power consumption below 5W.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Firmware power management; hardware support</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Firmware Engineering; Sustainability Team</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+          <t>Enable Automatic Firmware Updates for Networked Printers</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,42 +513,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Update Management</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+          <t>Implement automatic firmware update functionality for printers connected to the network, allowing updates to be applied without manual intervention.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security requirements.</t>
+          <t>Reduces manual workload for IT administrators and ensures printers remain secure and up-to-date.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware attacks, improves compliance with industry standards, and increases customer trust in device security.</t>
+          <t>Improved security posture, reduced maintenance effort, and enhanced reliability for enterprise customers.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Printers should update seamlessly in the background without disrupting user workflows.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Embedded controller firmware; Secure Boot implementation; signature verification at boot.</t>
+          <t>All networked printers within enterprise environments.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware must reject unsigned images and boot only signed firmware.</t>
+          <t>Automatic updates enabled for at least 80% of supported models.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of shipped devices support Secure Boot for embedded controller firmware.</t>
+          <t>Achieve 95% automatic update adoption across supported printer models.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Secure Boot infrastructure; signing tools; hardware support for signature verification.</t>
+          <t>Network connectivity; Firmware update server availability</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Platform Security Team; Embedded Controller Firmware Team</t>
+          <t>Firmware Team; IT Admins</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optimize Power Management for Sleep Mode</t>
+          <t>Add Support for Secure Boot in Printer Firmware</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improve firmware handling of sleep mode to minimize power consumption while maintaining wake responsiveness.</t>
+          <t>Integrate secure boot functionality into printer firmware to prevent unauthorized code execution during startup.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Extends battery life and meets customer expectations for efficient power usage in portable devices.</t>
+          <t>Addresses critical security vulnerabilities and aligns with enterprise security requirements.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Longer battery runtime, reduced energy costs, and improved user satisfaction.</t>
+          <t>Enhanced device security, compliance with industry standards, and reduced risk of firmware tampering.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Device should wake quickly from sleep without noticeable delay.</t>
+          <t>Printers should boot securely and reliably, with no impact on normal operation.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Firmware power management routines; sleep/wake transitions; battery-powered devices.</t>
+          <t>All new printer models released in 2025 and later.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sleep mode power draw must not exceed 0.5W.</t>
+          <t>Secure boot enabled and validated on all new models.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve sleep mode power draw of 0.3W or less.</t>
+          <t>Secure boot implemented with zero false positives or boot failures.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,89 +630,1673 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hardware power rails; OS sleep signals; battery management IC.</t>
+          <t>Hardware support for secure boot; Firmware integration</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Power Management Firmware Team; Hardware Engineering</t>
+          <t>Firmware Team; Security Engineering</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Support for Multi-Language Error Messages</t>
+          <t>Improve Printer Wake-Up Time from Sleep Mode</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Ruiz</t>
+          <t>Raj Patel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Optimize firmware to reduce the time required for printers to wake up from sleep mode and become ready for printing.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Enhances user experience and productivity, especially in high-volume office environments.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Faster response times, reduced user wait, and improved satisfaction.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Printers should wake up quickly and reliably when a print job is sent.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>All enterprise printer models with sleep mode functionality.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Wake-up time ≤ 10 seconds for 80% of models.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wake-up time ≤ 5 seconds for all models.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Firmware optimization; Hardware readiness</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Firmware Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Provide Detailed Error Logging in Firmware</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Samantha Lee</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enhance firmware to log detailed error information for troubleshooting and support purposes.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Improves support efficiency and enables faster issue resolution.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reduced downtime, improved customer satisfaction, and easier root cause analysis.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Error logs should be accessible to support staff without impacting printer operation.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>All enterprise printer models.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Error logging enabled for all critical errors.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Comprehensive error logging with minimal performance impact.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Firmware logging subsystem</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Firmware Team; Support Engineering</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Enable Automatic Firmware Updates for Networked Printers</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Implement automatic firmware update capability for all networked printers to ensure devices are always running the latest approved firmware.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reduces manual intervention, ensures security patches and feature updates are deployed promptly, and minimizes device downtime.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Improved device reliability, enhanced security posture, and reduced IT maintenance workload.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Users should not need to manually check or install firmware updates; updates should occur seamlessly in the background.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>All networked printers managed within enterprise environments.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Automatic updates enabled for at least 90% of deployed printers.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Achieve 100% automatic firmware update coverage for networked printers.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Network connectivity; Firmware update server availability</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>IT Operations; Firmware Engineering</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Add Secure Boot Support to Embedded Controller</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Integrate secure boot functionality into the embedded controller firmware to prevent unauthorized code execution during device startup.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Protects devices from firmware-level attacks and ensures only trusted code is executed, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Enhanced device security, compliance with regulatory requirements, and reduced risk of malicious firmware.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Device startup should be secure and transparent to end users, with no impact on boot time.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware for all enterprise printer models.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Secure boot enabled and validated on all new devices.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Secure boot implemented across all embedded controllers with zero boot failures.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Trusted Platform Module (TPM); Secure firmware signing infrastructure</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Team</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Improve Firmware Logging for Remote Diagnostics</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alex Chen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enhance firmware logging capabilities to support remote diagnostics and troubleshooting by IT administrators.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Enables faster issue resolution, reduces need for onsite support, and improves device uptime.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lower support costs, improved customer satisfaction, and more actionable diagnostic data.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Administrators should be able to access detailed logs remotely without impacting device performance.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Firmware logging subsystem for all enterprise printers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Remote log access enabled for at least 80% of deployed devices.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Comprehensive remote logging with minimal performance overhead.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Remote access infrastructure; Logging subsystem enhancements</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>IT Support; Firmware Diagnostics Team</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Support Multi-Language User Interface in Firmware</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Localization</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Implement multi-language support for firmware error messages to improve accessibility for global users.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Addresses international market needs and reduces support calls due to unclear error communication.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Better user experience for non-English speakers, increased global adoption, and fewer misunderstandings.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Users should see error messages in their preferred language as set in device settings.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Firmware error handling; language selection logic; message translation.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Support for English, Spanish, French, and German error messages.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Support for 10+ languages in firmware error messages.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Translation files; language selection mechanism; QA for localization.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Localization Team; Firmware QA</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Add multi-language support to the printer firmware user interface to accommodate global users.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Expands market reach, improves accessibility, and enhances user satisfaction in non-English speaking regions.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Broader adoption, improved usability, and compliance with international requirements.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language during device setup or operation.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Firmware UI for all enterprise printer models.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Support for at least five major languages.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Full localization for all supported languages with consistent UI experience.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Localization resources; UI framework updates</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware UI Engineering</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Enable Automatic Firmware Updates for Networked Printers</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Implement automatic firmware update functionality for all networked printers to ensure devices are always running the latest firmware.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Reduces manual intervention, improves security posture, and ensures consistent device performance across the fleet.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Minimizes downtime, lowers support costs, and enhances customer satisfaction by keeping devices up-to-date automatically.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Users should not need to manually check or initiate firmware updates; updates should occur seamlessly in the background.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>All networked printers managed via HP fleet management tools.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Automatic updates enabled for 90% of networked printers.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Achieve 100% automatic firmware update coverage for networked printers.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Fleet management tools; network connectivity; firmware update server</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Firmware team; IT management; Network Operations</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Add Secure Boot Support for Embedded Controller</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Integrate secure boot functionality into the embedded controller firmware to prevent unauthorized code execution.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Protects devices from malicious firmware attacks and ensures only trusted code is executed during boot.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enhances device security, reduces risk of compromise, and meets enterprise compliance requirements.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Device should boot securely and reliably, with no impact to user experience.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware for all Victoria program devices.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Secure boot enabled and validated on all embedded controllers.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Secure boot passes all compliance and penetration tests.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Hardware support for secure boot; firmware signing infrastructure</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Security team; Embedded controller hardware team</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Improve Printer Wake-Up Time from Sleep Mode</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Optimize firmware to reduce the time required for printers to wake up from sleep mode and become ready for printing.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Improves user productivity and reduces perceived latency when initiating print jobs.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Faster response times, improved customer satisfaction, and competitive differentiation.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Printer should wake up quickly and reliably when a print job is sent or a user interacts with the device.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>All Victoria program printers with sleep mode functionality.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Wake-up time ≤ 10 seconds from sleep mode.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Wake-up time ≤ 5 seconds from sleep mode.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Power management subsystem; firmware optimization</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Firmware team; Power management team</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Support Multi-Language User Interface on Printer LCD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Maria Lopez</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Add support for multiple languages in the printer LCD user interface to accommodate global users.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Enhanced user experience, increased adoption in international markets, and reduced support calls.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language easily during setup or from settings.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Printer LCD UI for all Victoria program devices.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Support for English, Spanish, French, and German.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Support for 10+ languages, including Asian and European languages.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Localization resources; UI firmware updates</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Localization team; Firmware UI team</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Implement Print Job Encryption for Sensitive Documents</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Add encryption for print jobs sent to printers to protect sensitive document data in transit.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Addresses enterprise security requirements and prevents data leakage during printing.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Improved compliance, reduced risk of data exposure, and increased trust from enterprise customers.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Users should not notice any delay or complexity when printing encrypted documents.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>All Victoria program printers handling sensitive documents.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Print job encryption enabled for all enterprise printers.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Encryption for all print jobs, with no impact to performance.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Encryption libraries; firmware integration; print server compatibility</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Security team; Firmware team; Enterprise IT</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Enable Automatic Firmware Updates for Networked Printers</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Implement automatic firmware update capability for all networked printers to ensure devices are always running the latest firmware.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Reduces manual intervention, improves device security, and ensures consistent performance across the fleet.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Minimizes downtime, lowers support costs, and enhances customer satisfaction by keeping devices up-to-date automatically.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Users should not need to manually check or install firmware updates; updates should occur seamlessly in the background.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>All networked printers within enterprise environments.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Automatic updates enabled for at least 90% of networked printers.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Achieve 100% automatic firmware update coverage for networked printers.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Network connectivity; Firmware update server availability</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Firmware Team; IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Add Secure Boot Support to Printer Firmware</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Integrate secure boot functionality into printer firmware to prevent unauthorized code execution during device startup.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Protects devices from malicious firmware and enhances overall security posture.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware tampering, increases customer trust, and meets enterprise security requirements.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Printers should boot only with verified firmware, ensuring device integrity.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>All new printer models released in 2025.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secure boot enabled and verified on all targeted models.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Secure boot implemented across all printer firmware platforms.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Hardware support for secure boot; Firmware signing infrastructure</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Firmware Team; Security Engineering; Hardware Team</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Improve Printer Wake-Up Time from Sleep Mode</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Optimize firmware to reduce the time required for printers to wake up from sleep mode and become ready for printing.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Enhances user experience by reducing wait times and increases productivity in high-volume environments.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Faster response times, improved workflow efficiency, and greater customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Printers should be ready to print within seconds of user interaction.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>All enterprise printer models with sleep mode functionality.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Wake-up time reduced to under 10 seconds.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wake-up time reduced to under 5 seconds.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Firmware optimization; Hardware readiness</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Firmware Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Support IPv6 Networking in Printer Firmware</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lisa Gomez</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Add IPv6 protocol support to printer firmware to enable compatibility with modern network infrastructures.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ensures future-proofing and compliance with enterprise IT standards.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Expands network compatibility, reduces configuration issues, and meets customer requirements for IPv6.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Printers should connect seamlessly to IPv6 networks without manual configuration.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>All network-capable printers.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IPv6 support enabled and verified on all network-capable printers.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Full IPv6 feature parity with IPv4.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Network stack updates; QA testing</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Firmware Team; Network Engineering</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Enable Automatic Firmware Updates for Networked Printers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Implement automatic firmware update functionality for networked printers to ensure devices are always running the latest firmware.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Reduces manual intervention, improves device security, and ensures consistent performance across the fleet.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Minimizes downtime, enhances security posture, and reduces IT support costs.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Users should not need to manually check or install firmware updates; updates should occur seamlessly.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Networked printers within enterprise environments.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Automatic updates enabled for at least 90% of networked printers.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Achieve 100% automatic firmware update coverage for all networked printers.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Network connectivity; Firmware update server availability</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>IT Admins; Firmware Engineering</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Add Support for Secure Boot in Printer Firmware</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Integrate secure boot functionality into printer firmware to prevent unauthorized code execution during device startup.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Protects devices from malicious firmware and enhances overall security compliance.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware tampering and ensures only trusted code runs on devices.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Printers should boot securely without noticeable delay or impact to user experience.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>All new printer models released in 2025.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Secure boot enabled and validated on all new models.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Secure boot implemented with zero boot failures.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Hardware support for secure boot; Firmware validation tools</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Security Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Improve Printer Sleep Recovery Time</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Optimize firmware to reduce the time required for printers to recover from sleep mode and become ready for printing.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Enhances user productivity and reduces perceived device lag.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Faster wake-up times lead to improved user satisfaction and reduced wait times.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Printers should be ready to print within seconds after waking from sleep.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>All enterprise printer models.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Recovery time from sleep ≤ 10 seconds.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Recovery time from sleep ≤ 5 seconds.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Firmware optimization; Hardware readiness</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; Hardware Team</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Support Multi-Language User Interface in Printer Firmware</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Add multi-language support to printer firmware user interface to accommodate global users.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Increases customer satisfaction and reduces support calls related to language barriers.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language easily during setup.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>All printers shipped to international markets.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Support for at least 5 major languages.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Support for 10+ languages with seamless switching.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Translation resources; UI framework updates</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware Engineering</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Enable Automatic Firmware Update Scheduling</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Allow users to schedule automatic firmware updates for their devices, providing flexibility in update timing.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Reduces manual intervention and ensures devices remain up-to-date, minimizing security risks and improving reliability.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Enhances user convenience and device security by automating firmware updates.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Users should be able to set preferred times for firmware updates, avoiding disruption during peak usage.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Firmware update scheduling functionality for all supported devices.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Scheduling feature available for at least 80% of device models.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>100% device coverage for firmware update scheduling.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Device firmware update subsystem; scheduling module integration</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; Platform Software Team</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Improve Firmware Boot Time</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Optimize firmware initialization routines to reduce overall device boot time.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Faster boot times improve user satisfaction and device competitiveness.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Shorter boot times lead to better user experience and increased productivity.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Devices should boot quickly and reliably, minimizing wait time for users.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Firmware boot sequence optimization for all device platforms.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Boot time reduced by at least 10% compared to previous release.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Boot time reduced by 20% or more.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Firmware initialization routines; hardware platform compatibility</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; Hardware Platform Team</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Add Support for Secure Firmware Rollback</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Michael Lee</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Implement secure rollback functionality to allow reverting to previous firmware versions without compromising device security.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Enables recovery from faulty updates while maintaining device integrity and security.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Reduces risk of device downtime and ensures secure recovery options.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Users should be able to safely revert firmware if issues arise, with no risk of security breaches.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Secure rollback support for all firmware versions and device models.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Rollback feature available for latest firmware versions.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Rollback feature available for all supported firmware versions.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Firmware version management; security validation routines</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; Security Team</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Provide Detailed Firmware Update Logs</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sarah Patel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Generate and store detailed logs for each firmware update, including success, failure, and error codes.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Improves troubleshooting and support efficiency by providing actionable update information.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reduces support costs and accelerates issue resolution.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Users and support teams should have access to comprehensive update logs for diagnostics.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Logging functionality for all firmware update processes.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Logs available for all update events; basic error codes included.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Logs include detailed error codes, timestamps, and update metadata.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Firmware update subsystem; logging infrastructure</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; Support Team</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>WANT</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Automatic Firmware Updates for Networked Printers</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,42 +513,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Update Management</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement automatic firmware update functionality for all networked printers to ensure devices remain up-to-date without manual intervention.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reduces IT overhead and ensures printers are secure and compliant with the latest features and patches.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Minimizes manual maintenance, improves device reliability, and enhances security posture.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should not need to manually check or install firmware updates; updates should occur seamlessly.</t>
+          <t>Users should experience seamless startup with assurance that their device is protected from threats.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>All networked printers managed within enterprise environments.</t>
+          <t>Implement Secure Boot verification in firmware for all supported hardware platforms.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Automatic updates enabled for 90% of deployed printers.</t>
+          <t>Secure Boot enabled and verified on all target devices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Achieve 100% automatic update coverage for networked printers.</t>
+          <t>100% Secure Boot coverage across Victoria platforms.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Network connectivity; Firmware update server availability</t>
+          <t>Hardware platform support; Trusted Platform Module integration</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IT Admins; Firmware Engineering; Network Operations</t>
+          <t>Platform Engineering; Security Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Support for WPA3 Security Protocol</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Update Process</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Integrate WPA3 wireless security protocol support into printer firmware to enhance network security.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Addresses evolving security standards and protects against vulnerabilities in older protocols.</t>
+          <t>Reduces operational disruption, increases customer satisfaction, and supports business continuity.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Improved wireless security, compliance with modern standards, and reduced risk of unauthorized access.</t>
+          <t>Faster updates, less impact on user productivity, and improved reliability of firmware deployment.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Printers should seamlessly connect to WPA3-enabled networks without user intervention.</t>
+          <t>Users should experience minimal interruption and clear progress indication during firmware updates.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All wireless-enabled printer models.</t>
+          <t>Revise update logic and scheduling to reduce downtime for Victoria devices.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WPA3 support available for new printer models.</t>
+          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WPA3 support for all wireless printers, including legacy models where feasible.</t>
+          <t>Achieve seamless updates with less than 1 minute downtime.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,69 +630,69 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Wireless chipset compatibility; Security library updates</t>
+          <t>Update server infrastructure; Firmware update logic</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Engineering; Security Team; Wireless Hardware Vendors</t>
+          <t>Firmware Team; IT Operations</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Improve Printer Boot Time</t>
+          <t>Add Multi-Language Support to Firmware UI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Carlos Ruiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Optimize firmware initialization routines to reduce printer boot time by at least 20%.</t>
+          <t>Integrate multi-language options into the firmware user interface to support global users.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enhances user experience and productivity by minimizing wait times after power-on or restart.</t>
+          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Faster device readiness, improved satisfaction, and reduced downtime.</t>
+          <t>Enhanced user satisfaction and increased adoption in international markets.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Printers should be ready to use within seconds of powering on.</t>
+          <t>Users should be able to select their preferred language during initial setup and in settings.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All printer models with boot time exceeding 60 seconds.</t>
+          <t>Implement language selection and translation for all UI elements in Victoria firmware.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Boot time reduced by 20% compared to current baseline.</t>
+          <t>Support for English, Spanish, French, and German in firmware UI.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Boot time under 45 seconds for all models.</t>
+          <t>Support for 10 languages in firmware UI.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Firmware optimization; Hardware initialization routines</t>
+          <t>Translation resources; UI framework compatibility</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Firmware Engineering; Hardware Team</t>
+          <t>Localization Team; Firmware UI Developers</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -719,52 +719,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Add Multi-Language Support for Printer UI</t>
+          <t>Enable Secure Boot for Firmware Updates</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maria Gonzalez</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Localization</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Expand firmware to support additional languages in printer user interface, including French, German, and Japanese.</t>
+          <t>Implement Secure Boot functionality to ensure only authenticated firmware updates are allowed.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enables broader market reach and improves accessibility for non-English speaking users.</t>
+          <t>Prevents unauthorized or malicious firmware from being installed, protecting device integrity.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enhanced usability, increased customer satisfaction, and expanded global sales opportunities.</t>
+          <t>Enhanced device security and compliance with enterprise standards.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Users should be able to select their preferred language during setup or from settings.</t>
+          <t>Users should not notice any change in update process unless an unauthorized update is attempted.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>All printers with display screens.</t>
+          <t>Applies to all firmware update mechanisms on Victoria platform.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Support for at least three new languages.</t>
+          <t>Secure Boot enabled for all firmware update paths.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Support for ten languages in total.</t>
+          <t>100% of firmware updates authenticated via Secure Boot.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -774,17 +774,161 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UI translation files; Localization QA</t>
+          <t>Firmware update infrastructure; Secure Boot module</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Firmware Engineering; Localization Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>WANT</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reduce Firmware Boot Time to Under 10 Seconds</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Optimize firmware initialization routines to achieve boot time under 10 seconds.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Improves user experience and meets competitive benchmarks for device responsiveness.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Faster device startup, increased customer satisfaction, and reduced support calls.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Users should experience noticeably faster device power-on and readiness.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Firmware boot sequence on Victoria platform.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 10 seconds in typical scenarios.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 8 seconds in all scenarios.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Firmware optimization; Hardware initialization routines</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Performance Engineering; Hardware Team</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics tools into firmware to allow service teams to access device health data.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Enables proactive support and reduces downtime by allowing remote troubleshooting.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lower service costs, improved uptime, and enhanced customer support experience.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Service teams can access diagnostics remotely without user intervention.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Victoria platform firmware; remote access interfaces.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Remote diagnostics accessible for basic health checks.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Full remote diagnostics including error logs and performance metrics.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Remote access infrastructure; Diagnostics module</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Service Engineering; IT Support</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
+          <t>Enhances platform security by preventing unauthorized code execution and protecting against malware at boot.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
+          <t>Reduces risk of firmware-level attacks, improves compliance with enterprise security standards, and increases customer trust.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should experience seamless startup with assurance that their device is protected from threats.</t>
+          <t>System should boot securely and transparently for end users, with no noticeable delay or complexity.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot verification in firmware for all supported hardware platforms.</t>
+          <t>Implement Secure Boot verification in firmware startup sequence; support for key management and signed firmware images.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all target devices.</t>
+          <t>Secure Boot enabled and verified for all production firmware images.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% Secure Boot coverage across Victoria platforms.</t>
+          <t>100% of shipped devices boot only trusted, signed firmware.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Hardware platform support; Trusted Platform Module integration</t>
+          <t>Firmware signing infrastructure; Key management system</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Platform Engineering; Security Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+          <t>Add Power Management Optimization for Sleep Mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Update Process</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+          <t>Optimize firmware handling of sleep mode to reduce power consumption and improve wake-up responsiveness.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reduces operational disruption, increases customer satisfaction, and supports business continuity.</t>
+          <t>Improves battery life and user satisfaction, aligning with sustainability goals and competitive benchmarks.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Faster updates, less impact on user productivity, and improved reliability of firmware deployment.</t>
+          <t>Longer device uptime, reduced energy costs, and enhanced user experience with faster wake times.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users should experience minimal interruption and clear progress indication during firmware updates.</t>
+          <t>Device should enter sleep mode quickly and resume operation instantly when prompted.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Revise update logic and scheduling to reduce downtime for Victoria devices.</t>
+          <t>Firmware changes to optimize sleep mode entry/exit, minimize power draw, and ensure reliable wake-up.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
+          <t>Sleep mode power consumption reduced by at least 20% compared to previous firmware.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve seamless updates with less than 1 minute downtime.</t>
+          <t>Achieve &lt;1W power draw in sleep mode; wake-up latency &lt;2 seconds.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,24 +630,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Update server infrastructure; Firmware update logic</t>
+          <t>Hardware power rails; OS sleep/wake signals</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Team; IT Operations</t>
+          <t>Hardware Engineering; OS Integration Team</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Multi-Language Support to Firmware UI</t>
+          <t>Support Multi-Language User Interface in Firmware</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -657,42 +657,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate multi-language options into the firmware user interface to support global users.</t>
+          <t>Add multi-language support to firmware user interface, enabling users to select their preferred language during setup.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
+          <t>Expands market reach and accessibility, supporting global customers and reducing support costs.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhanced user satisfaction and increased adoption in international markets.</t>
+          <t>Improved user satisfaction, reduced onboarding friction, and increased adoption in non-English speaking regions.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Users should be able to select their preferred language during initial setup and in settings.</t>
+          <t>Users should be able to select their language easily during initial setup and change it later in settings.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Implement language selection and translation for all UI elements in Victoria firmware.</t>
+          <t>Firmware UI changes to support multiple languages; language selection and persistence.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Support for English, Spanish, French, and German in firmware UI.</t>
+          <t>Support for at least 5 major languages in firmware UI.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Support for 10 languages in firmware UI.</t>
+          <t>Full localization for top 10 languages by market share.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Translation resources; UI framework compatibility</t>
+          <t>Translation assets; UI framework updates</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -717,198 +717,86 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Enable Secure Boot for Firmware Updates</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>John Smith</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Implement Secure Boot functionality to ensure only authenticated firmware updates are allowed.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Prevents unauthorized or malicious firmware from being installed, protecting device integrity.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Enhanced device security and compliance with enterprise standards.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Users should not notice any change in update process unless an unauthorized update is attempted.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Applies to all firmware update mechanisms on Victoria platform.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Secure Boot enabled for all firmware update paths.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>100% of firmware updates authenticated via Secure Boot.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Firmware update infrastructure; Secure Boot module</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Security Engineering; Platform Firmware Team</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reduce Firmware Boot Time to Under 10 Seconds</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Emily Chen</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Optimize firmware initialization routines to achieve boot time under 10 seconds.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Improves user experience and meets competitive benchmarks for device responsiveness.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Faster device startup, increased customer satisfaction, and reduced support calls.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Users should experience noticeably faster device power-on and readiness.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Firmware boot sequence on Victoria platform.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Boot time ≤ 10 seconds in typical scenarios.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Boot time ≤ 8 seconds in all scenarios.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Firmware optimization; Hardware initialization routines</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Performance Engineering; Hardware Team</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Add Remote Diagnostics Capability</t>
+          <t>Enable Secure Boot for Firmware Updates</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serviceability</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Integrate remote diagnostics tools into firmware to allow service teams to access device health data.</t>
+          <t>Implement Secure Boot functionality to ensure only authenticated firmware updates are allowed.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Enables proactive support and reduces downtime by allowing remote troubleshooting.</t>
+          <t>Prevents unauthorized firmware modifications, enhancing device security and compliance.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lower service costs, improved uptime, and enhanced customer support experience.</t>
+          <t>Reduces risk of malicious firmware, protects customer data, and meets enterprise security standards.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Service teams can access diagnostics remotely without user intervention.</t>
+          <t>Firmware updates should be seamless and secure, with no impact on user experience.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Victoria platform firmware; remote access interfaces.</t>
+          <t>Applies to all firmware update mechanisms across supported devices.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Remote diagnostics accessible for basic health checks.</t>
+          <t>Secure Boot enabled for all firmware updates.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Full remote diagnostics including error logs and performance metrics.</t>
+          <t>100% of firmware updates authenticated via Secure Boot.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -918,17 +806,89 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Remote access infrastructure; Diagnostics module</t>
+          <t>Firmware update infrastructure; Secure Boot implementation</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Service Engineering; IT Support</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Optimize Power Consumption During Idle State</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Power Management</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Reduce power draw when device is in idle state by optimizing firmware routines.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Improves battery life and reduces operational costs for end users.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enhanced energy efficiency, longer device uptime, and lower environmental impact.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Device should remain responsive while minimizing power usage during idle.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Idle state power management across all device models.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Idle power consumption ≤ 0.5W.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Idle power consumption ≤ 0.3W.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Hardware power management; Firmware idle routines</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Hardware Engineering; Power Management Team</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution and protecting against malware at boot.</t>
+          <t>Enhances platform security by preventing unauthorized code execution at boot, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware-level attacks, improves compliance with enterprise security standards, and increases customer trust.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in platform security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>System should boot securely and transparently for end users, with no noticeable delay or complexity.</t>
+          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot verification in firmware startup sequence; support for key management and signed firmware images.</t>
+          <t>Implement Secure Boot verification in firmware; support standard Secure Boot keys.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified for all production firmware images.</t>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of shipped devices boot only trusted, signed firmware.</t>
+          <t>Full Secure Boot compliance with industry standards.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware signing infrastructure; Key management system</t>
+          <t>Platform hardware support; Secure Boot key provisioning</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Power Management Optimization for Sleep Mode</t>
+          <t>Firmware Update Rollback Protection</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimize firmware handling of sleep mode to reduce power consumption and improve wake-up responsiveness.</t>
+          <t>Prevent firmware from being downgraded to previous versions to protect against vulnerabilities.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves battery life and user satisfaction, aligning with sustainability goals and competitive benchmarks.</t>
+          <t>Maintains system integrity by ensuring only approved firmware versions are installed, reducing exposure to known issues.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Longer device uptime, reduced energy costs, and enhanced user experience with faster wake times.</t>
+          <t>Improves reliability and security, minimizes risk from outdated firmware.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Device should enter sleep mode quickly and resume operation instantly when prompted.</t>
+          <t>Firmware update process should notify users if rollback is attempted and block the action.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Firmware changes to optimize sleep mode entry/exit, minimize power draw, and ensure reliable wake-up.</t>
+          <t>Block installation of older firmware versions; provide user feedback on rollback attempts.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption reduced by at least 20% compared to previous firmware.</t>
+          <t>Rollback protection active on all firmware update paths.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve &lt;1W power draw in sleep mode; wake-up latency &lt;2 seconds.</t>
+          <t>No successful rollback to vulnerable firmware versions.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hardware power rails; OS sleep/wake signals</t>
+          <t>Firmware update mechanism; version tracking</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hardware Engineering; OS Integration Team</t>
+          <t>Firmware Update Team; Security Engineering</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -647,52 +647,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Support Multi-Language User Interface in Firmware</t>
+          <t>Add Power Management Logging</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Ruiz</t>
+          <t>Raj Patel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Localization</t>
+          <t>Diagnostics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Add multi-language support to firmware user interface, enabling users to select their preferred language during setup.</t>
+          <t>Integrate logging for power management events in firmware to aid troubleshooting and performance analysis.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Expands market reach and accessibility, supporting global customers and reducing support costs.</t>
+          <t>Provides visibility into power management behavior, enabling faster diagnosis of issues and optimization.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Improved user satisfaction, reduced onboarding friction, and increased adoption in non-English speaking regions.</t>
+          <t>Reduces troubleshooting time, improves platform reliability, supports proactive maintenance.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Users should be able to select their language easily during initial setup and change it later in settings.</t>
+          <t>Logs should be accessible via standard diagnostic tools without impacting system performance.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Firmware UI changes to support multiple languages; language selection and persistence.</t>
+          <t>Log all major power management events; ensure logs are retrievable post-reboot.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Support for at least 5 major languages in firmware UI.</t>
+          <t>Power management logging enabled and verified.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Full localization for top 10 languages by market share.</t>
+          <t>Comprehensive event logging with minimal performance impact.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Translation assets; UI framework updates</t>
+          <t>Firmware logging subsystem; diagnostic tool integration</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Localization Team; Firmware UI Developers</t>
+          <t>Diagnostics Team; Power Management Engineering</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>WANT</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enable Secure Boot for Firmware Updates</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -766,37 +766,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Implement Secure Boot functionality to ensure only authenticated firmware updates are allowed.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prevents unauthorized firmware modifications, enhancing device security and compliance.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reduces risk of malicious firmware, protects customer data, and meets enterprise security standards.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Firmware updates should be seamless and secure, with no impact on user experience.</t>
+          <t>Users should experience seamless startup with no noticeable delays or interruptions.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Applies to all firmware update mechanisms across supported devices.</t>
+          <t>Implement Secure Boot validation in firmware for all bootable devices.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Secure Boot enabled for all firmware updates.</t>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>100% of firmware updates authenticated via Secure Boot.</t>
+          <t>100% Secure Boot coverage for all firmware-supported devices.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Firmware update infrastructure; Secure Boot implementation</t>
+          <t>Platform hardware support; Trusted Platform Module integration</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team</t>
+          <t>Security Engineering; Platform Hardware Team</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Optimize Power Consumption During Idle State</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,42 +833,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Update Process</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reduce power draw when device is in idle state by optimizing firmware routines.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Improves battery life and reduces operational costs for end users.</t>
+          <t>Reduces operational disruption and increases customer satisfaction by shortening update windows.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhanced energy efficiency, longer device uptime, and lower environmental impact.</t>
+          <t>Faster updates lead to higher productivity and less impact on business operations.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Device should remain responsive while minimizing power usage during idle.</t>
+          <t>Users should experience minimal interruption and clear progress indication during firmware updates.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Idle state power management across all device models.</t>
+          <t>Optimize update logic, reduce reboot cycles, and enhance progress reporting.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Idle power consumption ≤ 0.5W.</t>
+          <t>Firmware updates complete within 5 minutes for standard configurations.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Idle power consumption ≤ 0.3W.</t>
+          <t>Achieve less than 3 minutes downtime for firmware updates.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -878,17 +878,89 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Hardware power management; Firmware idle routines</t>
+          <t>Firmware update infrastructure; Platform OS integration</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hardware Engineering; Power Management Team</t>
+          <t>Firmware Development; Platform Software Team</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Add Support for New Peripheral Device in Firmware</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Michael Lee</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Integrate support for the new XYZ peripheral device in the firmware.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Expands device compatibility, enabling broader market reach and customer adoption.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Allows customers to use new peripherals without manual configuration or compatibility issues.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Plug-and-play experience for the new peripheral device.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Firmware-level integration and validation for XYZ peripheral.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Peripheral recognized and functional on first connection.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Full compatibility with XYZ peripheral device.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Peripheral hardware specifications; Driver integration</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Peripheral Vendor; Firmware QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support in Firmware</t>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+          <t>Add Secure Boot functionality to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution at boot, aligning with enterprise security standards.</t>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware and unauthorized access, improves customer trust in platform security.</t>
+          <t>Reduces risk of firmware attacks, improves customer trust, and meets compliance requirements for secure hardware platforms.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
+          <t>System startup should be seamless and secure, with no noticeable delay or impact to end users.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot verification in firmware; support standard Secure Boot keys.</t>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all supported platforms.</t>
+          <t>Secure Boot enabled and verified on all production firmware images.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Full Secure Boot compliance with industry standards.</t>
+          <t>100% of shipped embedded controller firmware images must pass Secure Boot verification.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Platform hardware support; Secure Boot key provisioning</t>
+          <t>Firmware signing infrastructure; Secure Boot verification logic; hardware support for Secure Boot.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team</t>
+          <t>Platform Security Team; Embedded Controller Firmware Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Firmware Update Rollback Protection</t>
+          <t>Optimize Power Management for Sleep Mode</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Prevent firmware from being downgraded to previous versions to protect against vulnerabilities.</t>
+          <t>Improve firmware algorithms to reduce power consumption during system sleep mode without impacting wake-up responsiveness.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maintains system integrity by ensuring only approved firmware versions are installed, reducing exposure to known issues.</t>
+          <t>Extends battery life and reduces energy consumption, supporting sustainability goals and enhancing user satisfaction.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Improves reliability and security, minimizes risk from outdated firmware.</t>
+          <t>Longer battery runtime, lower operational costs, and improved environmental impact.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Firmware update process should notify users if rollback is attempted and block the action.</t>
+          <t>Users should experience faster wake-up times and longer battery life during sleep mode.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Block installation of older firmware versions; provide user feedback on rollback attempts.</t>
+          <t>Firmware power management routines; sleep mode optimization; wake-up responsiveness.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Rollback protection active on all firmware update paths.</t>
+          <t>Sleep mode power consumption reduced by at least 10% compared to previous firmware version.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No successful rollback to vulnerable firmware versions.</t>
+          <t>Achieve minimum 15% reduction in sleep mode power usage while maintaining wake-up time under 2 seconds.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,69 +630,69 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Firmware update mechanism; version tracking</t>
+          <t>Power management firmware modules; hardware power states; battery subsystem.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Update Team; Security Engineering</t>
+          <t>Firmware Power Team; Hardware Power Engineering; System Integration</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Power Management Logging</t>
+          <t>Add Multi-Language Support to Device Status Display</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Carlos Ruiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate logging for power management events in firmware to aid troubleshooting and performance analysis.</t>
+          <t>Implement multi-language support for device status messages displayed on the firmware-controlled LCD panel.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Provides visibility into power management behavior, enabling faster diagnosis of issues and optimization.</t>
+          <t>Improves accessibility and usability for global customers, supporting international market expansion.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reduces troubleshooting time, improves platform reliability, supports proactive maintenance.</t>
+          <t>Enhanced user experience for non-English speakers, increased market reach, and reduced support calls.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Logs should be accessible via standard diagnostic tools without impacting system performance.</t>
+          <t>Device status messages should be clearly displayed in the user's selected language.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Log all major power management events; ensure logs are retrievable post-reboot.</t>
+          <t>Firmware display routines; LCD panel messaging; language selection logic.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Power management logging enabled and verified.</t>
+          <t>Support for English, French, German, Spanish, and Japanese device status messages.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Comprehensive event logging with minimal performance impact.</t>
+          <t>Support at least 10 languages for device status display with accurate translations.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Firmware logging subsystem; diagnostic tool integration</t>
+          <t>Translation database; firmware display logic; LCD hardware.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Diagnostics Team; Power Management Engineering</t>
+          <t>Localization Team; Firmware Display Team; QA Translation Verification</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>WANT</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Users should experience seamless startup with no noticeable delays or interruptions.</t>
+          <t>Users should experience seamless startup with no impact on boot time or usability.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>100% Secure Boot coverage for all firmware-supported devices.</t>
+          <t>100% Secure Boot coverage with no user intervention required.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Hardware Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+          <t>Firmware Update Rollback Capability</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,42 +833,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Update Process</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+          <t>Provide a mechanism in firmware to rollback to the previous version if a firmware update fails or causes issues.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reduces operational disruption and increases customer satisfaction by shortening update windows.</t>
+          <t>Improves device reliability and reduces downtime by allowing recovery from failed updates.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Faster updates lead to higher productivity and less impact on business operations.</t>
+          <t>Minimizes risk of bricked devices, enhances customer satisfaction, and reduces support costs.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Users should experience minimal interruption and clear progress indication during firmware updates.</t>
+          <t>Users should be able to recover from failed updates without technical assistance.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Optimize update logic, reduce reboot cycles, and enhance progress reporting.</t>
+          <t>Support rollback for all firmware updates on supported platforms.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Firmware updates complete within 5 minutes for standard configurations.</t>
+          <t>Rollback mechanism functional and tested for all update scenarios.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Achieve less than 3 minutes downtime for firmware updates.</t>
+          <t>Zero failed updates resulting in unrecoverable devices.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -878,89 +878,2657 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Firmware update infrastructure; Platform OS integration</t>
+          <t>Firmware update infrastructure; Storage partitioning</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Firmware Development; Platform Software Team</t>
+          <t>Platform Firmware Team; QA</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>WANT</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Add Power Management Optimization</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Optimize firmware power management routines to reduce energy consumption during idle and active states.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Supports sustainability goals and extends device battery life, meeting customer expectations.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lower operational costs, improved battery performance, and reduced environmental impact.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Users should notice longer battery life and cooler device operation.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Apply power management optimizations across all supported device states.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Demonstrated reduction in power consumption compared to previous firmware.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Achieve at least 10% reduction in average power usage.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Hardware power states; Firmware routines</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Platform Engineering; Hardware Team</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Support Multi-Language Error Messaging</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Implement multi-language support for firmware error messages to improve accessibility for global users.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves user experience for non-English speakers.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Reduces confusion, increases satisfaction, and supports international deployments.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Users should receive error messages in their preferred language.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Add multi-language support for all firmware error messages.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>All error messages available in top 5 supported languages.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Full localization coverage for error messaging.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Localization resources; Firmware messaging framework</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware Engineering</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Automated Firmware Health Monitoring</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Integrate automated health monitoring in firmware to detect and report anomalies during operation.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Enables proactive maintenance and reduces device failures by early detection of issues.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Improved reliability, reduced support incidents, and enhanced customer trust.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Users should not notice monitoring unless an issue is detected and reported.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monitor key firmware metrics and report anomalies automatically.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Health monitoring active and reporting verified anomalies.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Detect and report 95% of critical firmware issues before failure.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Firmware telemetry; Reporting infrastructure</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>QA; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Enhances device security by preventing unauthorized code execution, aligning with industry standards for secure platforms.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Users should experience seamless startup with assurance that their device is protected from threats.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot verification process within firmware; support for key management and validation.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all production units.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage for all firmware images shipped.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Firmware cryptographic libraries; hardware root of trust</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ensures better customer experience and operational efficiency by reducing interruptions caused by firmware updates.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Shorter update windows, less impact on productivity, increased customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Firmware updates should be unobtrusive and require minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Revise update logic to support incremental updates and rollback capabilities.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Update process completes within 5 minutes for standard devices.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Achieve less than 2 minutes downtime per firmware update.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Update server infrastructure; device connectivity</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; QA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Add Multi-Language Support to Firmware UI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>User Interface</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Integrate multi-language options into the firmware user interface to support global customers.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Enhanced usability and inclusivity, increased customer satisfaction in international markets.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language during device setup.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Add language selection menu and localization for all UI elements.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Support for English, Spanish, French, and German in UI.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Support for 10 languages in firmware UI.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Localization resources; UI framework</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Localization Team; UI Engineering</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, improves compliance with industry security requirements, and increases customer trust.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>System startup should be seamless and secure, with no noticeable impact to end-user experience.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Firmware must reject unsigned images and log failure events.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>100% of shipped embedded controller firmware supports Secure Boot and signature verification.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Secure Boot infrastructure; Firmware signing tools; Platform BIOS integration</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform BIOS Team; Embedded Controller Firmware Team</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Add Battery Health Reporting to System Firmware</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Implement battery health status reporting in system firmware, exposing metrics such as cycle count, capacity, and degradation to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Provides critical diagnostic information for proactive maintenance and warranty support, reducing downtime and improving customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Enables predictive maintenance, reduces warranty costs, and enhances user trust in device reliability.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Users and IT admins should be able to view battery health metrics in OS utilities and management consoles.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>System firmware; battery health metric collection; interface to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Battery health metrics are available via standard OS APIs and management tools.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Report cycle count, capacity, and health status with &gt;95% accuracy.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Battery firmware; OS integration; Management tool support</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Battery Engineering; System Firmware Team; IT Management Software Team</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Support Fan Speed Control via UEFI Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Thermal Management</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Allow users to configure fan speed profiles through UEFI firmware settings, enabling custom thermal management based on usage scenarios.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Empowers users to optimize system performance and acoustics, addressing diverse needs from silent operation to maximum cooling.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Improves user satisfaction, reduces thermal complaints, and supports flexible deployment in various environments.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Users can select or customize fan profiles in UEFI without requiring OS-level tools.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UEFI firmware; fan speed profile configuration; user interface in UEFI setup.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>At least three selectable fan profiles available in UEFI settings.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Provide silent, balanced, and performance fan profiles with real-time adjustment.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Fan controller firmware; UEFI setup interface; Hardware support for variable fan speeds</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Thermal Engineering; UEFI Firmware Team; Hardware Design Team</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Users should experience seamless startup with no noticeable delays or interruptions.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot in firmware for all Victoria platform devices.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all Victoria devices.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage with zero boot failures.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Platform hardware support; Trusted Platform Module integration</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Hardware Team</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ensures business continuity and reduces disruption for end users during firmware updates.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Faster updates, less operational impact, improved customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Firmware updates should be unobtrusive and require minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Victoria platform firmware update process.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Update downtime reduced to less than 2 minutes per device.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Achieve seamless updates with zero user complaints.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; Network reliability</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Firmware Team; IT Operations</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carlos Martinez</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics tools into firmware to allow support teams to troubleshoot devices without physical access.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Improves support efficiency and reduces time to resolution for customer issues.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lower support costs, faster issue resolution, enhanced customer experience.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Support teams can access diagnostic information remotely with secure authentication.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Victoria platform devices with network connectivity.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Remote diagnostics accessible for 95% of support cases.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Full remote diagnostics coverage for all Victoria devices.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Network connectivity; Secure authentication mechanisms</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Support Engineering; Firmware Team</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot functionality in the Embedded Controller firmware to ensure only signed firmware images are loaded during device startup.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Enhances device security by preventing unauthorized or malicious firmware from executing, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, improves customer trust, and meets compliance requirements for secure device operation.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Device startup should be seamless and secure, with no noticeable delay or user intervention required.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Embedded Controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified for all production firmware images.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>100% of production devices ship with Secure Boot enabled and functioning.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; Secure Boot keys management; Embedded Controller hardware support.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Firmware Team; Platform Hardware Team</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Add Battery Health Reporting to System Firmware</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Integrate battery health status reporting into system firmware, providing real-time health metrics accessible via OS and diagnostic tools.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Improves device maintainability and user awareness, enabling proactive battery replacement and reducing unexpected failures.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Enhanced user experience, reduced support costs, and improved device reliability.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Users and IT admins can easily view battery health status through standard interfaces without additional software.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>System firmware; battery health metrics; OS and diagnostic tool integration.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Battery health metrics available and accurate for all supported battery types.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Battery health reporting accuracy &gt;95%; accessible via OS APIs.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Battery firmware interface; OS integration; diagnostic tool updates.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>System Firmware Team; Battery Engineering; OS Integration Team</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Support Fast Charging Detection in Firmware</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Power Management</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Update firmware to detect and report fast charging capability when compatible chargers are connected.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Enables users to maximize charging speed and efficiency, supporting competitive device features.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Improved charging experience, reduced downtime, and differentiation in the market.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Device should notify users when fast charging is active, with clear indication in UI.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Firmware charger detection logic; fast charging status reporting; UI integration.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Fast charging detection works reliably with all supported chargers.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Detection latency &lt;2 seconds; 100% accuracy for supported chargers.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Charger hardware compatibility; firmware detection algorithms; UI integration.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Firmware Team; Charger Hardware Team; UI/UX Team</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Implement Thermal Event Logging in Platform Firmware</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sara Lee</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Add logging of thermal events (overheating, throttling, shutdowns) to platform firmware for post-event analysis.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Supports root cause analysis and improves device reliability by enabling detailed thermal event tracking.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Faster troubleshooting, reduced warranty claims, and improved product quality.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thermal events are logged automatically and accessible to support teams without impacting user experience.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Platform firmware; thermal sensor integration; event logging; log retrieval interfaces.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Thermal events are logged with timestamp and severity; logs retrievable via standard tools.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Log all thermal events with &lt;1 second latency; logs available for all supported devices.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Thermal sensors; firmware logging subsystem; support tool integration.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Platform Firmware Team; Thermal Engineering; Support Tools Team</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Provide Firmware-Based Fan Speed Control Profiles</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Michael Brown</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thermal Management</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Develop firmware profiles for fan speed control based on device usage scenarios (e.g., performance, quiet, balanced).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Allows users and IT admins to optimize device cooling and acoustics, improving satisfaction and device longevity.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Customizable cooling, reduced noise, and improved thermal performance.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Users can select fan profiles easily; device responds dynamically to profile changes.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Firmware fan control algorithms; profile selection interface; integration with OS and management tools.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>All profiles function as intended; fan speed adjusts according to selected profile.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Profile switching latency &lt;1 second; accurate fan speed control for all scenarios.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Fan hardware interface; firmware control logic; OS and management tool integration.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Firmware Team; Thermal Engineering; OS Integration Team</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution and protecting against malware at boot.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Improved system integrity and compliance with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Users should experience seamless boot with no interruptions or warnings unless unauthorized firmware is detected.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot verification for all firmware components loaded during startup.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified for all firmware modules.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>100% of firmware modules verified and loaded only if signed and trusted.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; Trusted Platform Module (TPM)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption and increases user satisfaction by shortening update windows.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Faster updates, less impact on productivity, and improved reliability.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Firmware updates should complete quickly with minimal user intervention and system downtime.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Optimize update logic, reduce reboot cycles, and streamline update validation.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Firmware update process completes within 5 minutes.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Firmware updates complete in under 2 minutes with no more than one reboot.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Update server infrastructure; Firmware validation tools</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Platform Firmware Team; IT Operations</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>MEDIUM WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Add Support for New Peripheral Device in Firmware</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Michael Lee</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Compatibility</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Integrate support for the new XYZ peripheral device in the firmware.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Expands device compatibility, enabling broader market reach and customer adoption.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Allows customers to use new peripherals without manual configuration or compatibility issues.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Plug-and-play experience for the new peripheral device.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Firmware-level integration and validation for XYZ peripheral.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Peripheral recognized and functional on first connection.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Full compatibility with XYZ peripheral device.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Peripheral hardware specifications; Driver integration</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Peripheral Vendor; Firmware QA</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>NICE TO HAVE</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Integrate support for the new XYZ peripheral device in the platform firmware.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Expands hardware compatibility and enables new use cases for customers.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Broader device support, increased customer satisfaction, and expanded market reach.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Peripheral device should be detected and function seamlessly without manual configuration.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Add drivers and initialization routines for XYZ peripheral device.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Peripheral device recognized and operational after firmware update.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Full functionality and performance parity with existing supported devices.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>XYZ device specifications; Driver development resources</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Hardware Engineering; Peripheral Vendor</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>LOW WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted code is executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution and protecting against rootkits.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Improved system integrity and compliance with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Users should experience seamless boot with no noticeable delay or interruptions.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot in firmware for all Victoria platform devices.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all Victoria devices.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage with no boot failures.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Platform hardware support; Trusted Platform Module integration</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption and increases user satisfaction during firmware maintenance.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Faster updates, less impact on productivity, and improved reliability.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Update process should be transparent and require minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Victoria platform firmware update workflow.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Downtime during update less than 2 minutes.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Downtime less than 1 minute for typical updates.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Update server infrastructure; Firmware update agent</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Platform Firmware Team; IT Operations</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Add Support for Multi-Language Error Messages</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Provide firmware error messages in multiple languages to improve accessibility.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Expands global usability and reduces support calls from non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Enhanced user experience and broader market reach.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Users should receive error messages in their preferred language based on system settings.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Victoria platform firmware error messaging system.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Support for English, Spanish, French, and German error messages.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Support for 10 languages.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Localization files; Language selection mechanism</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Localization Team; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure hardware platforms.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Firmware must reject unsigned images and log failure.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>100% of shipped units enforce Secure Boot for embedded controller firmware.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Secure Boot infrastructure; Firmware signing tools; Embedded controller hardware support.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Platform Security Team; Embedded Controller Firmware Team</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Increase Firmware Update Speed for Platform Devices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Optimize firmware update process to reduce total update time for platform devices by at least 30%.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Improves customer satisfaction and reduces downtime during maintenance, supporting faster deployment cycles.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Shorter update windows, improved device availability, and enhanced user experience during firmware upgrades.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Users should experience minimal disruption and faster completion of firmware updates.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Platform device firmware update routines; update delivery mechanisms.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Update time reduced by at least 30% compared to previous baseline.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Achieve firmware update completion within 5 minutes for all supported devices.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; Device communication protocols.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; Platform Device Engineering</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics functionality into firmware to allow support teams to access device health and logs remotely.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Enables proactive support and reduces need for onsite visits, improving service efficiency and reducing operational costs.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Faster issue resolution, improved customer support experience, and lower service costs.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Support teams can remotely access diagnostic information without user intervention.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Firmware diagnostics modules; remote access protocols; log retrieval.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Remote diagnostics accessible for all supported devices.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Enable remote diagnostics for 100% of deployed devices.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Remote access infrastructure; Diagnostic data formats.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Support Engineering; Firmware Diagnostics Team</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during device startup.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Enhances device security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure device operation.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Device startup should be seamless and secure, with no noticeable delay or impact to end-user experience.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Firmware must reject unsigned images and boot only signed firmware.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>100% of shipped devices enforce Secure Boot for embedded controller firmware.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cryptographic signing infrastructure; Secure Boot verification logic; Firmware update process.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Firmware Team; Platform Validation</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Add Battery Health Reporting to System Firmware</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Implement battery health status reporting in system firmware, exposing metrics such as cycle count, capacity, and degradation to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Provides actionable insights for IT admins and end users, enabling proactive maintenance and reducing downtime.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Improved device reliability, reduced warranty claims, and enhanced user satisfaction through transparent battery health information.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Users and IT admins should be able to view battery health metrics in system tools without additional software.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>System firmware; battery health metrics collection; interface to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Battery health metrics are available and accurate for all supported battery types.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Battery health reporting covers 95%+ of deployed devices and is accessible via standard OS interfaces.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Battery firmware; OS integration; Management tool support.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>System Firmware Team; Battery Engineering; IT Management Solutions</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Support Fast Boot Option in BIOS Setup</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Introduce a Fast Boot option in BIOS setup to minimize POST time by skipping non-essential hardware checks.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Improves user experience by reducing device boot time, making devices more competitive in performance-sensitive markets.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Faster boot times, increased productivity, and enhanced perception of device responsiveness.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Users should be able to enable Fast Boot in BIOS and experience noticeably quicker startup.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BIOS setup interface; POST sequence optimization; hardware check configuration.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Fast Boot option is available and reduces boot time by at least 20%.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Boot time reduced by 30% when Fast Boot is enabled.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>BIOS firmware; hardware initialization routines.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>BIOS Firmware Team; Hardware Validation</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Integrate TPM 2.0 Support in Platform Firmware</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lisa Wong</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Add support for TPM 2.0 in platform firmware to enable advanced security features such as BitLocker and secure credential storage.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Meets industry requirements for device security, enabling compliance with enterprise and government standards.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Enhanced device security, broader market access, and improved customer confidence.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TPM features should be available and functional without user intervention.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Platform firmware; TPM 2.0 integration; OS interface support.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TPM 2.0 is detected and functional in all supported devices.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>TPM 2.0 support validated across all device configurations.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>TPM hardware; platform firmware; OS integration.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Platform Firmware Team; Security Engineering; OS Integration</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Provide Firmware Update Rollback Capability</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Michael Brown</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Update Management</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Implement firmware update rollback functionality, allowing users to revert to a previous firmware version if issues are detected.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Reduces risk of device outages due to faulty updates, improves supportability, and enhances customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Minimized downtime, faster recovery from update failures, and improved trust in firmware update process.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Users should be able to initiate rollback easily via standard update tools.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Firmware update process; rollback logic; user interface integration.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Rollback capability is available for all firmware updates.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Rollback process completes successfully in 99% of cases without data loss.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; version management; user interface.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; Support Engineering; QA</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized or malicious code from running at boot, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure platforms.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot validation in firmware; support for key management and signed firmware images.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage across all Victoria platforms.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Platform hardware support for Secure Boot; signed firmware image infrastructure.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Hardware Team</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption for customers, making firmware updates less intrusive and more reliable.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Faster updates, improved customer satisfaction, and lower support costs due to fewer update-related issues.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Users should experience minimal interruption during firmware updates, ideally with no noticeable downtime.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Revise update workflow; implement staged update and rollback capabilities.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Achieve seamless firmware updates with zero downtime for end users.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Update infrastructure; rollback mechanism; QA validation.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Firmware QA; Platform Operations</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to collect logs and status remotely.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Enables proactive support and troubleshooting, reducing time to resolution and improving customer experience.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lower support costs, faster issue resolution, and improved reliability through early detection of problems.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Support teams can access diagnostic information remotely without requiring user intervention.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Implement remote log collection and status reporting in firmware; secure access controls.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Remote diagnostics available and functional on all Victoria devices.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Full remote diagnostics coverage with secure access.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Network connectivity; secure access infrastructure.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Support Engineering; Security Team</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support in Firmware</t>
+          <t>Enable Secure Boot for Firmware Updates</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+          <t>Implement Secure Boot functionality to ensure only signed firmware updates are accepted and installed.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution, meeting enterprise compliance requirements.</t>
+          <t>Prevents unauthorized firmware modifications, protecting device integrity and user data.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware and unauthorized access, improves customer trust in platform security.</t>
+          <t>Enhanced device security, compliance with enterprise standards, reduced risk of malware.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should experience seamless startup with no impact on boot time or usability.</t>
+          <t>Users should have confidence that firmware updates are authentic and safe.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot validation in firmware for all bootable devices.</t>
+          <t>Applies to all firmware update mechanisms; covers validation and enforcement of signed updates.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all supported platforms.</t>
+          <t>Signed firmware updates enforced for all devices.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% Secure Boot coverage for all boot paths.</t>
+          <t>100% of firmware updates validated via Secure Boot.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Platform hardware support; OS compatibility; Key management infrastructure</t>
+          <t>Firmware signing infrastructure; Secure Boot implementation</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team; OS Integration Team</t>
+          <t>Security Engineering; Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+          <t>Optimize Firmware Boot Time</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+          <t>Reduce firmware boot time to improve device startup experience.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reduces operational disruption for customers, supporting business continuity and positive user experience.</t>
+          <t>Faster boot times enhance user satisfaction and device competitiveness.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Faster updates, less downtime, improved customer satisfaction.</t>
+          <t>Improved user experience, reduced wait times, better market positioning.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Firmware updates should be unobtrusive and require minimal user intervention.</t>
+          <t>Device should be ready for use within seconds of power-on.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All supported platforms and update scenarios.</t>
+          <t>Firmware initialization routines; hardware interaction optimization.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Firmware update process completes with less than 5 minutes downtime.</t>
+          <t>Boot time ≤ 10 seconds.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Downtime during firmware update &lt; 2 minutes.</t>
+          <t>Boot time ≤ 5 seconds.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Update delivery infrastructure; Platform compatibility</t>
+          <t>Hardware initialization; Firmware optimization</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Update Team; QA; Platform Engineering</t>
+          <t>Firmware Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -647,52 +647,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Support for New Peripheral Device in Firmware</t>
+          <t>Add Remote Diagnostics Capability</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Ruiz</t>
+          <t>Carlos Rivera</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Serviceability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate support for the new XYZ peripheral device in platform firmware.</t>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to access device logs and status remotely.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Expands platform capabilities and market reach by supporting new hardware.</t>
+          <t>Enables proactive support and faster issue resolution, reducing downtime.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enables customers to use latest peripherals, increasing platform versatility.</t>
+          <t>Lower support costs, improved customer satisfaction, faster troubleshooting.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peripheral should be plug-and-play with no manual configuration required.</t>
+          <t>Support teams can access diagnostic information without requiring user intervention.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Firmware support for XYZ device across all relevant platforms.</t>
+          <t>Remote access to logs, status, and error codes; secure communication required.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Peripheral recognized and functional on all supported platforms.</t>
+          <t>Remote diagnostics accessible for all devices.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Full compatibility and seamless operation with XYZ device.</t>
+          <t>Diagnostics available within 2 minutes of request.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,17 +702,233 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Peripheral hardware specifications; Driver integration</t>
+          <t>Remote communication protocol; Firmware logging</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Peripheral Vendor; Platform Firmware Team</t>
+          <t>Support Engineering; Firmware Team</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure device operation.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Users should not notice any change in device operation, but benefit from improved security.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all production firmware images.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>100% of shipped embedded controller firmware supports Secure Boot.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; Secure Boot keys management; Embedded controller hardware compatibility.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Firmware Team; Platform Hardware Team</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Optimize Power Consumption During Sleep Mode</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Power Management</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Reduce power draw of the platform during sleep mode by optimizing firmware routines and hardware interactions.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Improves battery life and energy efficiency, supporting sustainability goals and enhancing user satisfaction.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Longer battery runtime, lower operational costs, and improved environmental impact.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Device should wake reliably from sleep while maximizing battery conservation.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Firmware sleep mode routines; hardware interface management; power state transitions.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sleep mode power consumption ≤ 0.5W.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sleep mode power consumption ≤ 0.3W.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Hardware power management ICs; OS sleep/wake signaling; Firmware optimization.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Platform Power Team; Firmware Development; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Add Support for USB-C Alternate Modes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Implement firmware support for USB-C alternate modes, including DisplayPort and Thunderbolt, to enable expanded connectivity options.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Expands device versatility and compatibility with modern peripherals, meeting customer expectations for connectivity.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Broader peripheral support, improved user experience, and increased device value.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Users can connect USB-C devices and seamlessly access alternate mode features.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USB-C firmware stack; alternate mode negotiation; DisplayPort and Thunderbolt support.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>USB-C alternate modes functional with certified peripherals.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Full compatibility with DisplayPort and Thunderbolt alternate modes.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USB-C hardware controller; Alternate mode protocol stacks; Peripheral certification.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Connectivity Engineering; Firmware Team; Peripheral Certification Lab</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>WANT</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot for Firmware Updates</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot functionality to ensure only signed firmware updates are accepted and installed.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prevents unauthorized firmware modifications, protecting device integrity and user data.</t>
+          <t>Enhances platform security by preventing unauthorized code execution at boot time.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enhanced device security, compliance with enterprise standards, reduced risk of malware.</t>
+          <t>Reduces risk of malware and unauthorized access, meeting enterprise security requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should have confidence that firmware updates are authentic and safe.</t>
+          <t>System should boot securely and transparently for end users.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Applies to all firmware update mechanisms; covers validation and enforcement of signed updates.</t>
+          <t>Implement Secure Boot verification in firmware for all supported hardware platforms.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Signed firmware updates enforced for all devices.</t>
+          <t>Secure Boot enabled and verified on all test platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of firmware updates validated via Secure Boot.</t>
+          <t>100% Secure Boot coverage for all Victoria-supported devices.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware signing infrastructure; Secure Boot implementation</t>
+          <t>Firmware cryptographic libraries; hardware TPM support</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Firmware Team</t>
+          <t>Platform Security Team; Hardware Engineering</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optimize Firmware Boot Time</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Update Process</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduce firmware boot time to improve device startup experience.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Faster boot times enhance user satisfaction and device competitiveness.</t>
+          <t>Ensures business continuity and reduces impact on end users during firmware maintenance.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Improved user experience, reduced wait times, better market positioning.</t>
+          <t>Faster updates, less disruption, improved user satisfaction.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Device should be ready for use within seconds of power-on.</t>
+          <t>Users should experience minimal interruption during firmware updates.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Firmware initialization routines; hardware interaction optimization.</t>
+          <t>Update firmware process logic to reduce downtime across all Victoria platforms.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Boot time ≤ 10 seconds.</t>
+          <t>Firmware update downtime reduced by at least 50% compared to previous release.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Boot time ≤ 5 seconds.</t>
+          <t>Achieve less than 2 minutes downtime per update.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hardware initialization; Firmware optimization</t>
+          <t>Firmware update subsystem; platform power management</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Team; Hardware Engineering</t>
+          <t>Firmware Engineering; QA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -647,52 +647,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Add Remote Diagnostics Capability</t>
+          <t>Add Multi-Language Support to Firmware UI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Rivera</t>
+          <t>Carlos Ruiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serviceability</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate remote diagnostics features into firmware to allow support teams to access device logs and status remotely.</t>
+          <t>Integrate multi-language capabilities into the firmware user interface.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enables proactive support and faster issue resolution, reducing downtime.</t>
+          <t>Expands market reach and improves accessibility for global users.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lower support costs, improved customer satisfaction, faster troubleshooting.</t>
+          <t>Enhanced user experience for non-English speakers, increased adoption.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Support teams can access diagnostic information without requiring user intervention.</t>
+          <t>Users should be able to select their preferred language during setup.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Remote access to logs, status, and error codes; secure communication required.</t>
+          <t>Support at least 5 major languages in firmware UI for Victoria platforms.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Remote diagnostics accessible for all devices.</t>
+          <t>Firmware UI available in English, Spanish, French, German, and Chinese.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Diagnostics available within 2 minutes of request.</t>
+          <t>Seamless language switching and localization.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,24 +702,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Remote communication protocol; Firmware logging</t>
+          <t>Firmware UI framework; translation assets</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Support Engineering; Firmware Team</t>
+          <t>Localization Team; Firmware UI Developers</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,37 +734,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure device operation.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Users should not notice any change in device operation, but benefit from improved security.</t>
+          <t>System startup should be seamless and secure, with no noticeable delay for end users.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+          <t>Implement Secure Boot in firmware for all Victoria platform devices.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all production firmware images.</t>
+          <t>Secure Boot enabled and verified on all Victoria devices.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>100% of shipped embedded controller firmware supports Secure Boot.</t>
+          <t>100% Secure Boot coverage across Victoria platform.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -774,24 +774,24 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Firmware signing infrastructure; Secure Boot keys management; Embedded controller hardware compatibility.</t>
+          <t>Trusted Platform Module (TPM); Firmware signing infrastructure</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Security Engineering; Embedded Controller Firmware Team; Platform Hardware Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Optimize Power Consumption During Sleep Mode</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -801,42 +801,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Update &amp; Maintenance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reduce power draw of the platform during sleep mode by optimizing firmware routines and hardware interactions.</t>
+          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Improves battery life and energy efficiency, supporting sustainability goals and enhancing user satisfaction.</t>
+          <t>Ensures business continuity and reduces disruption for end users during firmware updates.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Longer battery runtime, lower operational costs, and improved environmental impact.</t>
+          <t>Shorter update windows, improved user satisfaction, and lower operational impact.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Device should wake reliably from sleep while maximizing battery conservation.</t>
+          <t>Firmware updates should be fast and unobtrusive, with minimal impact on device availability.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Firmware sleep mode routines; hardware interface management; power state transitions.</t>
+          <t>Victoria platform firmware update process.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption ≤ 0.5W.</t>
+          <t>Firmware update downtime reduced to less than 2 minutes per device.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption ≤ 0.3W.</t>
+          <t>Achieve seamless firmware updates with less than 1 minute downtime.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Hardware power management ICs; OS sleep/wake signaling; Firmware optimization.</t>
+          <t>Firmware update infrastructure; Device management tools</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Platform Power Team; Firmware Development; Hardware Engineering</t>
+          <t>Platform Firmware Team; IT Operations</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Add Support for USB-C Alternate Modes</t>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -873,42 +873,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Diagnostics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Implement firmware support for USB-C alternate modes, including DisplayPort and Thunderbolt, to enable expanded connectivity options.</t>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to access device health and logs remotely.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Expands device versatility and compatibility with modern peripherals, meeting customer expectations for connectivity.</t>
+          <t>Improves support efficiency and reduces time to resolution for customer issues.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Broader peripheral support, improved user experience, and increased device value.</t>
+          <t>Faster troubleshooting, reduced need for onsite visits, and improved customer satisfaction.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Users can connect USB-C devices and seamlessly access alternate mode features.</t>
+          <t>Support teams should be able to access diagnostics remotely without impacting device performance.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>USB-C firmware stack; alternate mode negotiation; DisplayPort and Thunderbolt support.</t>
+          <t>Victoria platform devices with network connectivity.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>USB-C alternate modes functional with certified peripherals.</t>
+          <t>Remote diagnostics accessible for support teams on Victoria devices.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Full compatibility with DisplayPort and Thunderbolt alternate modes.</t>
+          <t>Comprehensive remote diagnostics with real-time log access.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -918,17 +918,233 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>USB-C hardware controller; Alternate mode protocol stacks; Peripheral certification.</t>
+          <t>Network connectivity; Support portal integration</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Connectivity Engineering; Firmware Team; Peripheral Certification Lab</t>
+          <t>Support Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution, meeting enterprise compliance requirements.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, increases customer trust in platform security.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>System should boot seamlessly with Secure Boot enabled, without impacting user experience.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot in firmware for all supported hardware platforms.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all target platforms.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Full Secure Boot support with no boot failures on compliant hardware.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Trusted Platform Module (TPM); UEFI firmware updates</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Platform Security Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ensures business continuity and reduces operational disruptions during firmware maintenance.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Faster updates, less downtime, improved customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Users should experience minimal interruption during firmware updates.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Optimize update process for all supported devices; target downtime reduction.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Firmware update downtime reduced by at least 50% compared to previous version.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Achieve less than 2 minutes downtime per update.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; device management tools</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Firmware Engineering; IT Operations</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Add Multi-Language Support to Firmware UI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>User Experience</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Integrate multi-language support into the firmware user interface to accommodate global users.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking customers.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Enhanced usability and satisfaction for international customers.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Users should be able to select their preferred language during initial setup.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Support at least 5 major languages in firmware UI.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Firmware UI available in English, Spanish, French, German, and Japanese.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Seamless language switching with full UI translation.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Localization resources; UI framework updates</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware UI Developers</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+          <t>Enable Secure Boot for Firmware Updates</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the embedded controller firmware to ensure only signed firmware images are executed.</t>
+          <t>Implement Secure Boot functionality to ensure only signed firmware updates are accepted and installed.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances device security by preventing unauthorized or malicious firmware from running on the embedded controller.</t>
+          <t>Prevents unauthorized firmware modifications, protecting device integrity and user data.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware attacks, increases customer trust, and meets enterprise security compliance requirements.</t>
+          <t>Enhanced device security, reduced risk of malware, and compliance with enterprise security standards.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Users should have confidence that firmware updates are authentic and safe.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures during boot.</t>
+          <t>Applies to all firmware update mechanisms on Victoria platform devices.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware must reject unsigned images and boot only signed firmware.</t>
+          <t>Firmware update process rejects unsigned images.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of shipped devices with embedded controller firmware supporting Secure Boot.</t>
+          <t>100% of firmware updates validated via Secure Boot.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Secure Boot infrastructure; signing tools; embedded controller hardware compatibility.</t>
+          <t>Firmware update subsystem; cryptographic signing infrastructure</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Embedded Controller Team; Platform Firmware Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot for Firmware Updates</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot functionality to ensure only signed firmware updates are accepted and installed.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prevents unauthorized firmware modifications, protecting device integrity and user data.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with industry standards for secure devices.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enhanced device security, reduced risk of malware, and compliance with enterprise security standards.</t>
+          <t>Reduces risk of malware and unauthorized access, increases customer trust in device security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should have confidence that firmware updates are authentic and safe.</t>
+          <t>Users should experience seamless startup with assurance that their device is protected from threats.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Applies to all firmware update mechanisms on Victoria platform devices.</t>
+          <t>Firmware changes to support Secure Boot, including integration with platform security modules.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware update process rejects unsigned images.</t>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% of firmware updates validated via Secure Boot.</t>
+          <t>Full Secure Boot compliance with industry standards.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Firmware update subsystem; cryptographic signing infrastructure</t>
+          <t>Platform security modules; OS bootloader compatibility</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -571,6 +571,166 @@
           <t>HIGH</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption for customers, making firmware updates less intrusive and more reliable.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Enhanced customer satisfaction due to faster updates and less impact on device availability.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Firmware updates should be quick and unobtrusive, with minimal interruption to device usage.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Update process optimization, including update packaging and installation routines.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Firmware update downtime reduced by at least 50% compared to current baseline.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Achieve near-zero downtime during firmware updates.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Update packaging tools; Device management systems</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; Device Management Team</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability to Firmware</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to troubleshoot devices without physical access.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Improves support efficiency and reduces need for onsite visits, lowering operational costs.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Faster issue resolution, improved customer experience, and reduced support costs.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Customers should be able to receive remote support without device downtime or manual intervention.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Firmware enhancements for remote diagnostics, including secure communication protocols.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Remote diagnostics available and functional for all supported devices.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Enable comprehensive remote diagnostics with secure access.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Support backend systems; Secure communication modules</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Support Engineering; Firmware Team</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jira/Fw_requirements.xlsx
+++ b/jira/Fw_requirements.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,32 +523,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution, aligning with industry standards for secure devices.</t>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with enterprise security standards.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware and unauthorized access, increases customer trust in device security.</t>
+          <t>Reduces risk of malware and unauthorized access, improves customer trust in device security.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Users should experience seamless startup with assurance that their device is protected from threats.</t>
+          <t>Users should experience seamless startup with no noticeable delays or interruptions.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Firmware changes to support Secure Boot, including integration with platform security modules.</t>
+          <t>Implement Secure Boot validation in firmware startup sequence.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all supported platforms.</t>
+          <t>Secure Boot enabled and passing validation tests.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Full Secure Boot compliance with industry standards.</t>
+          <t>100% of shipped devices support Secure Boot.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Platform security modules; OS bootloader compatibility</t>
+          <t>Firmware validation tools; Trusted Platform Module integration</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Update</t>
+          <t>Update Management</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Improve the firmware update mechanism to minimize device downtime during updates.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reduces operational disruption for customers, making firmware updates less intrusive and more reliable.</t>
+          <t>Reduces operational disruption for customers, increasing satisfaction and adoption rates.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enhanced customer satisfaction due to faster updates and less impact on device availability.</t>
+          <t>Faster updates, less impact on productivity, improved reliability.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Firmware updates should be quick and unobtrusive, with minimal interruption to device usage.</t>
+          <t>Users should experience minimal interruption and clear progress indication during firmware updates.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Update process optimization, including update packaging and installation routines.</t>
+          <t>Revise update logic to reduce downtime and provide user feedback.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Firmware update downtime reduced by at least 50% compared to current baseline.</t>
+          <t>Downtime during update ≤ 2 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Achieve near-zero downtime during firmware updates.</t>
+          <t>Downtime during update ≤ 1 minute.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Update packaging tools; Device management systems</t>
+          <t>Update delivery infrastructure; Firmware update engine</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Update Team; Device Management Team</t>
+          <t>Platform Firmware Team; QA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carlos Rivera</t>
+          <t>Carlos Martinez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -662,37 +662,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Integrate remote diagnostics features into firmware to allow support teams to troubleshoot devices without physical access.</t>
+          <t>Integrate remote diagnostics features into firmware to allow support teams to access device health and logs remotely.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Improves support efficiency and reduces need for onsite visits, lowering operational costs.</t>
+          <t>Improves support efficiency and reduces time to resolution for customer issues.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Faster issue resolution, improved customer experience, and reduced support costs.</t>
+          <t>Enables proactive maintenance, reduces need for onsite visits, lowers support costs.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Customers should be able to receive remote support without device downtime or manual intervention.</t>
+          <t>Users should be able to authorize remote diagnostics easily and securely.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Firmware enhancements for remote diagnostics, including secure communication protocols.</t>
+          <t>Add remote access APIs and secure log retrieval mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Remote diagnostics available and functional for all supported devices.</t>
+          <t>Remote diagnostics accessible and logs retrievable by support.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Enable comprehensive remote diagnostics with secure access.</t>
+          <t>Full remote diagnostics with real-time health monitoring.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Support backend systems; Secure communication modules</t>
+          <t>Remote access infrastructure; Security protocols</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -732,6 +732,1998 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with industry standards.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, increases customer trust in device security.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>System startup should be seamless and secure, with no noticeable delay for end users.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot validation in firmware for all bootable devices.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage for all bootable devices.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Platform hardware support; Trusted Platform Module (TPM); OS compatibility</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Platform Engineering; Security Team; OS Vendors</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption and enhances user satisfaction by shortening update windows.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Faster updates lead to higher productivity and less frustration for end users.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Firmware updates should be unobtrusive and require minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>All supported platforms and devices requiring firmware updates.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Firmware update downtime reduced by at least 50% compared to previous version.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Achieve less than 2 minutes downtime per firmware update.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Firmware update infrastructure; Device drivers; Network reliability</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Firmware Team; IT Operations; QA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Add Support for Multi-Language Error Messages in Firmware</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enable firmware to display error messages in multiple languages based on user settings.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Improves accessibility and user experience for global customers.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reduces support calls and increases satisfaction among non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Users should see error messages in their preferred language without manual configuration.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>All error messages generated by firmware across supported platforms.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Firmware supports at least 5 major languages for error messages.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Full localization coverage for all firmware error messages.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Localization libraries; User profile management; Translation resources</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Firmware Team; Localization Team; QA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution at boot time.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, meeting enterprise security requirements.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>System should boot securely and transparently for end users.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Integrate Secure Boot into firmware; validate compatibility with existing hardware.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>100% Secure Boot coverage across Victoria platforms.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Hardware compatibility; Secure Boot keys management</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Platform Security Team; Hardware Engineering</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Improve firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Reduces operational disruption and increases customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Faster updates, less impact on productivity, improved reliability.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Users should experience minimal interruption during firmware updates.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Revise update workflow; implement incremental update support.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Downtime per update &lt; 2 minutes.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Downtime per update &lt; 1 minute.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Update server infrastructure; firmware packaging</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Firmware Team; IT Operations</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Add Multi-Language Support to Firmware UI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>User Experience</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Implement multi-language options in firmware user interface to support global users.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Expands market reach and improves accessibility for non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Enhanced user satisfaction and increased adoption in international markets.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Users can select preferred language during setup and operation.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Add language selection feature; translate UI elements.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Support for English, Spanish, French, German.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Support for 10+ languages.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Translation resources; UI framework compatibility</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Localization Team; Firmware UI Developers</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot for Firmware Updates</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot functionality to ensure only authenticated firmware updates are applied to the device.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Prevents unauthorized firmware modifications, protecting device integrity and user data.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Enhanced device security, reduced risk of malware, and compliance with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Users should have confidence that firmware updates are safe and verified.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Applies to all firmware update mechanisms on Victoria platform.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled for all firmware updates.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>100% of firmware updates authenticated via Secure Boot.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Firmware update subsystem; Secure Boot implementation</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Security Engineering; Firmware Team</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Boot Time</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Reduce firmware boot time to improve device startup experience.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Faster boot times enhance user satisfaction and device competitiveness.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Improved user experience, reduced wait times, and better market positioning.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Device should boot quickly and reliably.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Firmware boot sequence optimization for Victoria platform.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 10 seconds.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Boot time ≤ 8 seconds.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bootloader; Firmware initialization routines</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Firmware Team; Performance Engineering</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Add Remote Diagnostics Capability</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Serviceability</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Integrate remote diagnostics features to allow support teams to access device logs and status remotely.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Enables proactive support and reduces downtime for end users.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Faster issue resolution, improved customer satisfaction, and lower support costs.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Support teams can access diagnostics without requiring user intervention.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Remote diagnostics for Victoria platform devices.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Remote access to basic device logs.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Full remote diagnostics including real-time status and error reporting.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Remote access subsystem; Logging framework</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Support Engineering; Firmware Team</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during device startup.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Enhances device security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware tampering, improves customer trust, and meets compliance requirements for secure device operation.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Device startup should be seamless and secure, with no noticeable delay or user intervention required.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; Key management for signing.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all production firmware images.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>100% of shipped devices boot only signed firmware images.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Key provisioning infrastructure; Firmware signing tools; Embedded controller hardware support.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Firmware Team; Manufacturing</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Add Battery Health Reporting to System Firmware</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Implement battery health status reporting in system firmware, exposing metrics such as cycle count, capacity, and degradation to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Provides actionable insights for IT admins and end users, enabling proactive maintenance and reducing unexpected battery failures.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Improved device reliability, reduced downtime, and enhanced user satisfaction through transparent battery health information.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Users and IT admins can easily access battery health data via OS utilities and management consoles.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>System firmware; Battery health metrics collection; Interface to OS and management tools.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Battery health metrics available and accurate for all supported battery types.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Report battery health with &gt;95% accuracy and update at least daily.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Battery hardware support; OS integration; Management tool APIs.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>System Firmware Team; Battery Hardware Team; IT Management Solutions</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Support Multi-Language Error Messaging in BIOS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Carlos Ruiz</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Enable BIOS error messages to be displayed in multiple languages based on user selection or region settings.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Improves accessibility and user experience for global customers, reducing support calls and misinterpretation of critical errors.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Enhanced customer satisfaction and reduced support costs through clear, localized error messaging.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Users receive BIOS error messages in their preferred language without manual configuration.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BIOS firmware; Error message localization; Language selection mechanism.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Support for at least 5 major languages in BIOS error messaging.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Support for 10+ languages with dynamic selection based on region or user preference.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Localization resources; BIOS UI framework; Regional language packs.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>BIOS Firmware Team; Localization Team; Regional QA</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during system startup.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reduces risk of firmware attacks, improves compliance with industry security requirements, and increases customer trust.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>System startup should be seamless and secure, with no noticeable delay or impact to end-user experience.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Embedded controller firmware; Secure Boot implementation; verification of firmware signatures at boot.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified for all production firmware images.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>100% of shipped embedded controller firmware supports Secure Boot with verified signatures.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; Secure Boot keys management; Embedded controller hardware compatibility.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Security Engineering; Embedded Controller Firmware Team; Platform Hardware Team</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Optimize Power Management for Sleep Mode</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Power Management</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Improve firmware handling of sleep mode to minimize power consumption while maintaining wake responsiveness.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Extends battery life and meets energy efficiency targets, critical for competitive positioning in mobile platforms.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Longer battery runtime, reduced energy costs, and improved user satisfaction with device standby performance.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Device should enter sleep mode quickly and resume instantly without user-perceptible lag.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sleep mode firmware routines; power state transitions; wake event handling.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sleep mode power consumption ≤ 0.5W; wake latency ≤ 2 seconds.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sleep mode power consumption ≤ 0.3W; wake latency ≤ 1 second.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Power management IC; OS power policy integration; hardware wake sources.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Firmware Power Team; Hardware Engineering; OS Integration</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Add Support for USB-C Alternate Modes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Raj Patel</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Implement firmware support for USB-C alternate modes, including DisplayPort and Thunderbolt, to enable expanded peripheral connectivity.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Supports modern connectivity standards, enabling compatibility with a wide range of devices and peripherals.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Enhanced user flexibility, improved device interoperability, and increased market appeal.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Users should be able to connect USB-C devices and peripherals seamlessly, with automatic detection and mode switching.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>USB-C firmware stack; alternate mode negotiation; peripheral compatibility.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>USB-C alternate modes functional for DisplayPort and Thunderbolt.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Full support for all USB-C alternate modes with automatic detection and switching.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USB-C hardware controller; alternate mode drivers; peripheral validation.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Connectivity Firmware Team; Hardware Validation; Peripheral Partners</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Improve Firmware Update Reliability</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sara Lee</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Update &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Enhance firmware update process to reduce failure rates and ensure robust rollback capability in case of update errors.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Minimizes risk of device bricking, improves customer satisfaction, and reduces support costs.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Higher update success rates, fewer support incidents, and improved brand reputation.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Firmware updates should complete successfully with clear user feedback and automatic recovery from errors.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Firmware update routines; error handling; rollback mechanisms.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Update failure rate &lt; 1%; rollback functional for all update scenarios.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Update failure rate &lt; 0.5%; seamless rollback with no user intervention.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Update infrastructure; rollback logic; QA testing.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; QA; Customer Support</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Support Multi-Language User Interface in Firmware</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Miguel Alvarez</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>User Experience</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Add multi-language support to firmware user interface, enabling users to select their preferred language during setup.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Expands global market reach and improves accessibility for non-English speaking users.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Greater customer satisfaction, increased adoption in international markets, and improved accessibility.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Users should be able to select and use their preferred language throughout device setup and operation.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Firmware UI strings; language selection logic; localization support.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Support for English, Spanish, French, and German in firmware UI.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Support for 10+ languages with seamless switching and full localization.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Localization resources; UI framework; translation validation.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Firmware UI Team; Localization Team; QA</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Enable Secure Boot Support in Firmware</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Enhances platform security by preventing unauthorized code execution, aligning with industry standards for secure systems.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Reduces risk of malware and unauthorized access, increases customer trust in device security.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>System startup should be seamless and secure, with no noticeable delay for end users.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Implement Secure Boot verification process in firmware; support for standard cryptographic algorithms.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Secure Boot enabled and verified on all production units.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>100% of shipped devices pass Secure Boot verification.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Cryptographic library integration; hardware root of trust</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Security Engineering; Platform Firmware Team</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ensures business continuity and user satisfaction by reducing interruptions caused by firmware updates.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Faster updates lead to higher productivity and less disruption for end users.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Firmware updates should be unobtrusive and require minimal user intervention.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Revise update logic to allow partial updates and rollback; optimize update scheduling.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Downtime during update does not exceed 2 minutes.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Downtime reduced to under 1 minute for typical updates.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Update server infrastructure; rollback mechanism</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Firmware Update Team; IT Operations</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
